--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_OLYMPIACOS PIRAEUS.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_OLYMPIACOS PIRAEUS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA44"/>
+  <dimension ref="A1:BA42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>225.8</v>
+        <v>370.48</v>
       </c>
       <c r="C2" t="n">
-        <v>228.86</v>
+        <v>372.9599999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>126.715022284366</v>
+        <v>123.6057486057486</v>
       </c>
       <c r="E2" t="n">
-        <v>94.38084418421744</v>
+        <v>97.06134706134708</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6361386138613861</v>
+        <v>0.6175548589341693</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1329163408913213</v>
+        <v>0.1430342328597311</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3</v>
+        <v>0.298780487804878</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1633663366336634</v>
+        <v>0.2100313479623825</v>
       </c>
       <c r="J2" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
       <c r="M2" t="n">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="N2" t="n">
+        <v>133</v>
+      </c>
+      <c r="O2" t="n">
+        <v>147</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.4608150470219436</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>26</v>
+      </c>
+      <c r="R2" t="n">
         <v>73</v>
       </c>
-      <c r="O2" t="n">
-        <v>79</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.3910891089108911</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>20</v>
-      </c>
-      <c r="R2" t="n">
-        <v>47</v>
-      </c>
       <c r="S2" t="n">
-        <v>0.2326732673267327</v>
+        <v>0.2288401253918495</v>
       </c>
       <c r="T2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U2" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05445544554455446</v>
+        <v>0.06583072100313479</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="X2" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0297029702970297</v>
+        <v>0.03761755485893417</v>
       </c>
       <c r="Z2" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="AA2" t="n">
-        <v>92</v>
+        <v>133</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.4554455445544555</v>
+        <v>0.4169278996865204</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.9240506329113924</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.425531914893617</v>
+        <v>0.3561643835616438</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AF2" t="n">
         <v>0.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.4360902255639098</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.848101265822785</v>
+        <v>1.80952380952381</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.316326530612245</v>
+        <v>1.324137931034483</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.7297297297297297</v>
+        <v>0.03636363636363636</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.066666666666667</v>
+        <v>0.04081632653061224</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>2</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AO2" t="n">
-        <v>5.941176470588236</v>
+        <v>5.316666666666666</v>
       </c>
       <c r="AP2" t="n">
-        <v>7.941176470588236</v>
+        <v>6.983333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75.26666666666667</v>
+        <v>74.09599999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>76.28666666666666</v>
+        <v>74.59199999999998</v>
       </c>
       <c r="D3" t="n">
-        <v>126.715022284366</v>
+        <v>123.6057486057486</v>
       </c>
       <c r="E3" t="n">
-        <v>94.38084418421744</v>
+        <v>97.06134706134709</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6361386138613861</v>
+        <v>0.6175548589341694</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1329163408913214</v>
+        <v>0.1430342328597311</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3</v>
+        <v>0.2987804878048781</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1633663366336634</v>
+        <v>0.2100313479623825</v>
       </c>
       <c r="J3" t="n">
-        <v>9</v>
+        <v>0.4</v>
       </c>
       <c r="K3" t="n">
-        <v>10.66666666666667</v>
+        <v>0.4</v>
       </c>
       <c r="L3" t="n">
-        <v>14</v>
+        <v>0.6</v>
       </c>
       <c r="M3" t="n">
-        <v>10.66666666666667</v>
+        <v>11.4</v>
       </c>
       <c r="N3" t="n">
-        <v>24.33333333333333</v>
+        <v>26.6</v>
       </c>
       <c r="O3" t="n">
-        <v>26.33333333333333</v>
+        <v>29.4</v>
       </c>
       <c r="P3" t="n">
-        <v>0.3910891089108911</v>
+        <v>0.4608150470219436</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.666666666666667</v>
+        <v>5.2</v>
       </c>
       <c r="R3" t="n">
-        <v>15.66666666666667</v>
+        <v>14.6</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2326732673267327</v>
+        <v>0.2288401253918495</v>
       </c>
       <c r="T3" t="n">
-        <v>1.333333333333333</v>
+        <v>1.8</v>
       </c>
       <c r="U3" t="n">
-        <v>3.666666666666667</v>
+        <v>4.2</v>
       </c>
       <c r="V3" t="n">
-        <v>0.05445544554455446</v>
+        <v>0.06583072100313481</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.02970297029702971</v>
+        <v>0.03761755485893417</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.33333333333333</v>
+        <v>11.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>30.66666666666667</v>
+        <v>26.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.4554455445544555</v>
+        <v>0.4169278996865204</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.9240506329113924</v>
+        <v>0.9047619047619049</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4255319148936171</v>
+        <v>0.3561643835616439</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AF3" t="n">
         <v>0.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.4347826086956522</v>
+        <v>0.4360902255639098</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.848101265822785</v>
+        <v>1.80952380952381</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.316326530612245</v>
+        <v>1.324137931034483</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.7297297297297297</v>
+        <v>0.03636363636363637</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.066666666666667</v>
+        <v>0.04081632653061224</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="AN3" t="n">
-        <v>2</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="AO3" t="n">
-        <v>5.941176470588235</v>
+        <v>5.316666666666666</v>
       </c>
       <c r="AP3" t="n">
-        <v>7.941176470588235</v>
+        <v>6.983333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>231.92</v>
+        <v>375.44</v>
       </c>
       <c r="C4" t="n">
-        <v>228.86</v>
+        <v>372.9599999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>94.38084418421744</v>
+        <v>97.06134706134708</v>
       </c>
       <c r="E4" t="n">
-        <v>126.715022284366</v>
+        <v>123.6057486057486</v>
       </c>
       <c r="F4" t="n">
-        <v>0.45</v>
+        <v>0.4647239263803681</v>
       </c>
       <c r="G4" t="n">
-        <v>0.144576430134417</v>
+        <v>0.1327091979538655</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2016806722689076</v>
+        <v>0.195</v>
       </c>
       <c r="I4" t="n">
-        <v>0.18</v>
+        <v>0.1809815950920245</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>48</v>
+      </c>
+      <c r="N4" t="n">
+        <v>108</v>
+      </c>
+      <c r="O4" t="n">
+        <v>140</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.4294478527607362</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>33</v>
+      </c>
+      <c r="R4" t="n">
+        <v>67</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.205521472392638</v>
+      </c>
+      <c r="T4" t="n">
+        <v>11</v>
+      </c>
+      <c r="U4" t="n">
+        <v>20</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.06134969325153374</v>
+      </c>
+      <c r="W4" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.07975460122699386</v>
+      </c>
+      <c r="Z4" t="n">
         <v>30</v>
       </c>
-      <c r="K4" t="n">
-        <v>27</v>
-      </c>
-      <c r="L4" t="n">
-        <v>27</v>
-      </c>
-      <c r="M4" t="n">
-        <v>32</v>
-      </c>
-      <c r="N4" t="n">
-        <v>66</v>
-      </c>
-      <c r="O4" t="n">
-        <v>88</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>25</v>
-      </c>
-      <c r="R4" t="n">
-        <v>48</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="T4" t="n">
-        <v>8</v>
-      </c>
-      <c r="U4" t="n">
-        <v>13</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>15</v>
-      </c>
       <c r="AA4" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.375</v>
+        <v>0.4049079754601227</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.75</v>
+        <v>0.7714285714285715</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.4925373134328358</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.55</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.25</v>
+        <v>0.3461538461538461</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.2</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.5</v>
+        <v>1.542857142857143</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.230769230769231</v>
+        <v>1.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.6206896551724138</v>
+        <v>0.740506329113924</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.8823529411764706</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.125</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.928571428571429</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.324324324324324</v>
+        <v>1.472727272727273</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.405405405405405</v>
+        <v>5.927272727272728</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.72972972972973</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>77.30666666666667</v>
+        <v>75.08799999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>76.28666666666666</v>
+        <v>74.59199999999998</v>
       </c>
       <c r="D5" t="n">
-        <v>94.38084418421744</v>
+        <v>97.06134706134709</v>
       </c>
       <c r="E5" t="n">
-        <v>126.715022284366</v>
+        <v>123.6057486057486</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4500000000000001</v>
+        <v>0.4647239263803681</v>
       </c>
       <c r="G5" t="n">
-        <v>0.144576430134417</v>
+        <v>0.1327091979538655</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2016806722689075</v>
+        <v>0.195</v>
       </c>
       <c r="I5" t="n">
-        <v>0.18</v>
+        <v>0.1809815950920245</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>10.66666666666667</v>
+        <v>9.6</v>
       </c>
       <c r="N5" t="n">
-        <v>22</v>
+        <v>21.6</v>
       </c>
       <c r="O5" t="n">
-        <v>29.33333333333333</v>
+        <v>28</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4400000000000001</v>
+        <v>0.4294478527607362</v>
       </c>
       <c r="Q5" t="n">
-        <v>8.333333333333334</v>
+        <v>6.6</v>
       </c>
       <c r="R5" t="n">
-        <v>16</v>
+        <v>13.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0.24</v>
+        <v>0.205521472392638</v>
       </c>
       <c r="T5" t="n">
-        <v>2.666666666666667</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>4.333333333333333</v>
+        <v>4</v>
       </c>
       <c r="V5" t="n">
-        <v>0.065</v>
+        <v>0.06134969325153374</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.06000000000000001</v>
+        <v>0.07975460122699386</v>
       </c>
       <c r="Z5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA5" t="n">
-        <v>25</v>
+        <v>26.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3750000000000001</v>
+        <v>0.4049079754601226</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.75</v>
+        <v>0.7714285714285715</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.4925373134328358</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.6153846153846154</v>
+        <v>0.55</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.25</v>
+        <v>0.3461538461538461</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.2</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.5</v>
+        <v>1.542857142857143</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.230769230769231</v>
+        <v>1.1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.6206896551724138</v>
+        <v>0.7405063291139241</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.8823529411764706</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.125</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.928571428571428</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.324324324324324</v>
+        <v>1.472727272727273</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.405405405405404</v>
+        <v>5.927272727272728</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.729729729729728</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="7">
@@ -1429,162 +1429,162 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>39</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
         <v>3</v>
       </c>
-      <c r="C8" t="n">
-        <v>27</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>23</v>
+      </c>
+      <c r="K8" t="n">
         <v>13</v>
       </c>
-      <c r="H8" t="n">
-        <v>3</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>4</v>
       </c>
-      <c r="J8" t="n">
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>13</v>
+      </c>
+      <c r="S8" t="n">
+        <v>12</v>
+      </c>
+      <c r="T8" t="n">
+        <v>64</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL8" t="n">
         <v>16</v>
       </c>
-      <c r="K8" t="n">
-        <v>6</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>41</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>3</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>13</v>
-      </c>
       <c r="AM8" t="n">
-        <v>0.615</v>
+        <v>0.625</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>136:25</t>
+          <t>115:27</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>18.76</v>
+        <v>27.64</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.857</v>
+        <v>0.895</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.857</v>
+        <v>0.901</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.439</v>
+        <v>1.411</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.16</v>
+        <v>0.217</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.214</v>
+        <v>0.263</v>
       </c>
       <c r="AU8" t="n">
-        <v>5.333</v>
+        <v>3.833</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.667</v>
+        <v>3.167</v>
       </c>
       <c r="AW8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.065</v>
+        <v>0.114</v>
       </c>
       <c r="AY8" t="n">
         <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.044</v>
+        <v>0.113</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.162</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="9">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AO9" t="n">
@@ -1740,10 +1740,10 @@
         <v>3</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.08</v>
+        <v>0.141</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.051</v>
+        <v>0.09</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -1759,162 +1759,162 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
+        <v>19</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>9</v>
+      </c>
+      <c r="F10" t="n">
         <v>2</v>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>15</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>7</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
         <v>2</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
         <v>2</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>32:39</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>1.88</v>
+        <v>19.76</v>
       </c>
       <c r="AP10" t="n">
-        <v>1</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.532</v>
+        <v>0.644</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.064</v>
+        <v>0.962</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>0.253</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.061</v>
+        <v>0.289</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>0.112</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.14</v>
+        <v>0.092</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="11">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="AO11" t="n">
@@ -2089,34 +2089,34 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E12" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -2131,120 +2131,120 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>9</v>
+      </c>
+      <c r="T12" t="n">
+        <v>80</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI12" t="n">
         <v>4</v>
       </c>
-      <c r="Q12" t="n">
-        <v>4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>6</v>
-      </c>
-      <c r="T12" t="n">
-        <v>55</v>
-      </c>
-      <c r="U12" t="n">
-        <v>10</v>
-      </c>
-      <c r="V12" t="n">
-        <v>9</v>
-      </c>
-      <c r="W12" t="n">
-        <v>4</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1</v>
-      </c>
       <c r="AJ12" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AK12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.389</v>
+        <v>0.4</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>169:46</t>
+          <t>121:02</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>43.32</v>
+        <v>68.08</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.632</v>
+        <v>0.619</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.649</v>
+        <v>0.636</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.177</v>
+        <v>1.16</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.092</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.079</v>
+        <v>0.102</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.5</v>
+        <v>9.833</v>
       </c>
       <c r="AW12" t="n">
-        <v>10.75</v>
+        <v>10.833</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.12</v>
+        <v>0.268</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.014</v>
+        <v>0.02</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.077</v>
+        <v>0.182</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.057</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="13">
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
@@ -2269,7 +2269,7 @@
         <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -2278,10 +2278,10 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
+        <v>8</v>
+      </c>
+      <c r="K13" t="n">
         <v>7</v>
-      </c>
-      <c r="K13" t="n">
-        <v>5</v>
       </c>
       <c r="L13" t="n">
         <v>3</v>
@@ -2296,19 +2296,19 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -2317,10 +2317,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -2353,7 +2353,7 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
@@ -2369,47 +2369,47 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>103:26</t>
+          <t>77:00</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.923</v>
+        <v>0.75</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.231</v>
+        <v>0.25</v>
       </c>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.333</v>
+        <v>2</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.333</v>
+        <v>3</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.667</v>
+        <v>5</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.059</v>
+        <v>0.099</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.035</v>
+        <v>0.048</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.049</v>
+        <v>0.091</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.068</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="14">
@@ -2419,162 +2419,162 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>3</v>
       </c>
       <c r="N14" t="n">
+        <v>6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>6</v>
+      </c>
+      <c r="R14" t="n">
         <v>3</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2</v>
-      </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="AB14" t="n">
         <v>5</v>
       </c>
       <c r="AC14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.556</v>
+        <v>0.417</v>
       </c>
       <c r="AE14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK14" t="n">
         <v>3</v>
       </c>
-      <c r="AG14" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1</v>
-      </c>
       <c r="AL14" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.1</v>
+        <v>0.167</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>127:06</t>
+          <t>87:19</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>28.88</v>
+        <v>51.4</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.4</v>
+        <v>0.366</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.386</v>
+        <v>0.396</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.104</v>
+        <v>0.117</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="AU14" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="AV14" t="n">
-        <v>8.333</v>
+        <v>6.833</v>
       </c>
       <c r="AW14" t="n">
-        <v>9.333</v>
+        <v>7.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.107</v>
+        <v>0.281</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>0.014</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.016</v>
+        <v>0.057</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.031</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="15">
@@ -2584,162 +2584,162 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>65</v>
+      </c>
+      <c r="D15" t="n">
+        <v>15</v>
+      </c>
+      <c r="E15" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" t="n">
+        <v>14</v>
+      </c>
+      <c r="I15" t="n">
+        <v>16</v>
+      </c>
+      <c r="J15" t="n">
+        <v>8</v>
+      </c>
+      <c r="K15" t="n">
+        <v>23</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>3</v>
       </c>
-      <c r="C15" t="n">
-        <v>32</v>
-      </c>
-      <c r="D15" t="n">
-        <v>7</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="Q15" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>12</v>
+      </c>
+      <c r="S15" t="n">
+        <v>13</v>
+      </c>
+      <c r="T15" t="n">
+        <v>90</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC15" t="n">
         <v>11</v>
       </c>
-      <c r="F15" t="n">
+      <c r="AD15" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF15" t="n">
         <v>3</v>
       </c>
-      <c r="G15" t="n">
+      <c r="AG15" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK15" t="n">
         <v>6</v>
       </c>
-      <c r="H15" t="n">
+      <c r="AL15" t="n">
         <v>9</v>
       </c>
-      <c r="I15" t="n">
+      <c r="AM15" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>89:38</t>
+        </is>
+      </c>
+      <c r="AO15" t="n">
+        <v>40.04</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.623</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="AV15" t="n">
         <v>10</v>
       </c>
-      <c r="J15" t="n">
-        <v>5</v>
-      </c>
-      <c r="K15" t="n">
-        <v>15</v>
-      </c>
-      <c r="L15" t="n">
-        <v>3</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7</v>
-      </c>
-      <c r="S15" t="n">
-        <v>6</v>
-      </c>
-      <c r="T15" t="n">
-        <v>45</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>3</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>71:11</t>
-        </is>
-      </c>
-      <c r="AO15" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0.748</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.368</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>8.5</v>
-      </c>
       <c r="AW15" t="n">
-        <v>11</v>
+        <v>12.667</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.154</v>
+        <v>0.213</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.051</v>
+        <v>0.054</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.212</v>
+        <v>0.257</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.052</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="16">
@@ -2749,82 +2749,82 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>37</v>
+      </c>
+      <c r="D16" t="n">
+        <v>15</v>
+      </c>
+      <c r="E16" t="n">
+        <v>26</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>7</v>
+      </c>
+      <c r="I16" t="n">
+        <v>11</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20</v>
+      </c>
+      <c r="L16" t="n">
+        <v>17</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
         <v>3</v>
       </c>
-      <c r="C16" t="n">
-        <v>23</v>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
         <v>3</v>
       </c>
-      <c r="I16" t="n">
-        <v>5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>5</v>
-      </c>
-      <c r="K16" t="n">
-        <v>7</v>
-      </c>
-      <c r="L16" t="n">
-        <v>9</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2</v>
-      </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="Z16" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="AB16" t="n">
         <v>2</v>
@@ -2839,10 +2839,10 @@
         <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG16" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
@@ -2864,47 +2864,47 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>125:04</t>
+          <t>97:00</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>19.2</v>
+        <v>32.84</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.625</v>
+        <v>0.577</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.632</v>
+        <v>0.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.198</v>
+        <v>1.127</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.052</v>
+        <v>0.061</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.188</v>
+        <v>0.269</v>
       </c>
       <c r="AU16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW16" t="n">
         <v>16</v>
       </c>
-      <c r="AW16" t="n">
-        <v>21</v>
-      </c>
       <c r="AX16" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.161</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.214</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.056</v>
+        <v>0.206</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.052</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="17">
@@ -2914,22 +2914,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F17" t="n">
         <v>4</v>
       </c>
-      <c r="E17" t="n">
-        <v>7</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3</v>
-      </c>
       <c r="G17" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H17" t="n">
         <v>6</v>
@@ -2938,135 +2938,135 @@
         <v>6</v>
       </c>
       <c r="J17" t="n">
+        <v>14</v>
+      </c>
+      <c r="K17" t="n">
+        <v>10</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>7</v>
+      </c>
+      <c r="R17" t="n">
+        <v>5</v>
+      </c>
+      <c r="S17" t="n">
         <v>9</v>
       </c>
-      <c r="K17" t="n">
-        <v>7</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
+      <c r="T17" t="n">
+        <v>44</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC17" t="n">
         <v>6</v>
       </c>
-      <c r="Q17" t="n">
-        <v>6</v>
-      </c>
-      <c r="R17" t="n">
+      <c r="AD17" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>85:09</t>
+        </is>
+      </c>
+      <c r="AO17" t="n">
+        <v>29.64</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AU17" t="n">
         <v>2</v>
       </c>
-      <c r="S17" t="n">
-        <v>8</v>
-      </c>
-      <c r="T17" t="n">
-        <v>36</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>2</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>95:02</t>
-        </is>
-      </c>
-      <c r="AO17" t="n">
-        <v>22.64</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0.607</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0.6909999999999999</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.016</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AV17" t="n">
-        <v>2.333</v>
+        <v>2.857</v>
       </c>
       <c r="AW17" t="n">
-        <v>3.833</v>
+        <v>4.857</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.112</v>
+        <v>0.166</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.074</v>
+        <v>0.117</v>
       </c>
       <c r="BA17" t="n">
         <v>0.09</v>
@@ -3079,40 +3079,40 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>19</v>
+      </c>
+      <c r="D18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" t="n">
+        <v>11</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>3</v>
       </c>
-      <c r="C18" t="n">
-        <v>15</v>
-      </c>
-      <c r="D18" t="n">
+      <c r="I18" t="n">
         <v>7</v>
-      </c>
-      <c r="E18" t="n">
-        <v>9</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="n">
-        <v>3</v>
       </c>
       <c r="J18" t="n">
         <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
         <v>4</v>
@@ -3121,46 +3121,46 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S18" t="n">
+        <v>6</v>
+      </c>
+      <c r="T18" t="n">
+        <v>39</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC18" t="n">
         <v>4</v>
-      </c>
-      <c r="T18" t="n">
-        <v>33</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2</v>
-      </c>
-      <c r="V18" t="n">
-        <v>4</v>
-      </c>
-      <c r="W18" t="n">
-        <v>5</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>7</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2</v>
       </c>
       <c r="AD18" t="n">
         <v>0.5</v>
@@ -3194,47 +3194,47 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>74:17</t>
+          <t>61:38</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>11.32</v>
+        <v>16.08</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.778</v>
+        <v>0.727</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.727</v>
+        <v>0.675</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.325</v>
+        <v>1.182</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.124</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.111</v>
+        <v>0.273</v>
       </c>
       <c r="AU18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV18" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>11</v>
+        <v>6.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.124</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.081</v>
+        <v>0.139</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.136</v>
+        <v>0.227</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.02</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="19">
@@ -3244,79 +3244,79 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" t="n">
+        <v>9</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" t="n">
+        <v>5</v>
+      </c>
+      <c r="J19" t="n">
+        <v>5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>6</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>5</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="n">
+        <v>33</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
         <v>11</v>
       </c>
-      <c r="F19" t="n">
-        <v>3</v>
-      </c>
-      <c r="G19" t="n">
-        <v>5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>3</v>
-      </c>
-      <c r="I19" t="n">
-        <v>3</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>3</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3</v>
-      </c>
-      <c r="T19" t="n">
-        <v>29</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" t="n">
-        <v>3</v>
-      </c>
-      <c r="W19" t="n">
-        <v>6</v>
-      </c>
-      <c r="X19" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>9</v>
-      </c>
       <c r="Z19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA19" t="n">
         <v>1</v>
@@ -3349,57 +3349,57 @@
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>57:22</t>
+        </is>
+      </c>
+      <c r="AO19" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.322</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AU19" t="n">
         <v>5</v>
       </c>
-      <c r="AM19" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>83:15</t>
-        </is>
-      </c>
-      <c r="AO19" t="n">
-        <v>17.32</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0.719</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.501</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.098</v>
+        <v>0.201</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.014</v>
+        <v>0.021</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.048</v>
+        <v>0.105</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.031</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="20">
@@ -3409,16 +3409,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -3427,22 +3427,22 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L20" t="n">
         <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -3451,19 +3451,19 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T20" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -3478,13 +3478,13 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Z20" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.8</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="AB20" t="n">
         <v>1</v>
@@ -3524,44 +3524,44 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>41:36</t>
+          <t>41:16</t>
         </is>
       </c>
       <c r="AO20" t="n">
-        <v>8.32</v>
+        <v>13.96</v>
       </c>
       <c r="AP20" t="n">
-        <v>0.6</v>
+        <v>0.571</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.633</v>
+        <v>0.639</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.962</v>
+        <v>1.003</v>
       </c>
       <c r="AS20" t="n">
-        <v>0.24</v>
+        <v>0.215</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.4</v>
+        <v>0.857</v>
       </c>
       <c r="AU20" t="n">
         <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.5</v>
+        <v>2.333</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.5</v>
+        <v>2.333</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.094</v>
+        <v>0.161</v>
       </c>
       <c r="AY20" t="n">
-        <v>0.058</v>
+        <v>0.059</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.097</v>
+        <v>0.17</v>
       </c>
       <c r="BA20" t="n">
         <v>0</v>
@@ -3574,79 +3574,79 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>81</v>
+      </c>
+      <c r="D21" t="n">
+        <v>9</v>
+      </c>
+      <c r="E21" t="n">
+        <v>18</v>
+      </c>
+      <c r="F21" t="n">
+        <v>18</v>
+      </c>
+      <c r="G21" t="n">
+        <v>39</v>
+      </c>
+      <c r="H21" t="n">
+        <v>9</v>
+      </c>
+      <c r="I21" t="n">
+        <v>11</v>
+      </c>
+      <c r="J21" t="n">
+        <v>21</v>
+      </c>
+      <c r="K21" t="n">
+        <v>21</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>11</v>
+      </c>
+      <c r="R21" t="n">
+        <v>9</v>
+      </c>
+      <c r="S21" t="n">
+        <v>13</v>
+      </c>
+      <c r="T21" t="n">
+        <v>91</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
+      </c>
+      <c r="V21" t="n">
+        <v>2</v>
+      </c>
+      <c r="W21" t="n">
         <v>3</v>
       </c>
-      <c r="C21" t="n">
-        <v>51</v>
-      </c>
-      <c r="D21" t="n">
-        <v>6</v>
-      </c>
-      <c r="E21" t="n">
-        <v>10</v>
-      </c>
-      <c r="F21" t="n">
-        <v>12</v>
-      </c>
-      <c r="G21" t="n">
-        <v>24</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3</v>
-      </c>
-      <c r="I21" t="n">
-        <v>4</v>
-      </c>
-      <c r="J21" t="n">
-        <v>13</v>
-      </c>
-      <c r="K21" t="n">
-        <v>14</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>3</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>6</v>
-      </c>
-      <c r="R21" t="n">
-        <v>5</v>
-      </c>
-      <c r="S21" t="n">
-        <v>5</v>
-      </c>
-      <c r="T21" t="n">
-        <v>58</v>
-      </c>
-      <c r="U21" t="n">
-        <v>11</v>
-      </c>
-      <c r="V21" t="n">
-        <v>5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>8</v>
-      </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Z21" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AA21" t="n">
         <v>1</v>
@@ -3655,10 +3655,10 @@
         <v>1</v>
       </c>
       <c r="AC21" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.25</v>
+        <v>0.111</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3679,57 +3679,57 @@
         <v>0.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AL21" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.5</v>
+        <v>0.459</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>129:29</t>
+          <t>120:49</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>41.76</v>
+        <v>72.84</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.706</v>
+        <v>0.632</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.713</v>
+        <v>0.655</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.221</v>
+        <v>1.112</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.144</v>
+        <v>0.151</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.158</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.167</v>
+        <v>1.909</v>
       </c>
       <c r="AV21" t="n">
-        <v>5.667</v>
+        <v>5.182</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.833</v>
+        <v>7.091</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.151</v>
+        <v>0.287</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.109</v>
+        <v>0.174</v>
       </c>
       <c r="BA21" t="n">
-        <v>0.146</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="22">
@@ -3739,49 +3739,49 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>10</v>
+      </c>
+      <c r="L22" t="n">
+        <v>5</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
         <v>3</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>6</v>
-      </c>
-      <c r="L22" t="n">
-        <v>3</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>2</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -3900,163 +3900,163 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>461</v>
+      </c>
+      <c r="D23" t="n">
+        <v>101</v>
+      </c>
+      <c r="E23" t="n">
+        <v>174</v>
+      </c>
+      <c r="F23" t="n">
+        <v>64</v>
+      </c>
+      <c r="G23" t="n">
+        <v>145</v>
+      </c>
+      <c r="H23" t="n">
+        <v>67</v>
+      </c>
+      <c r="I23" t="n">
+        <v>92</v>
+      </c>
+      <c r="J23" t="n">
+        <v>100</v>
+      </c>
+      <c r="K23" t="n">
+        <v>161</v>
+      </c>
+      <c r="L23" t="n">
+        <v>49</v>
+      </c>
+      <c r="M23" t="n">
+        <v>27</v>
+      </c>
+      <c r="N23" t="n">
+        <v>18</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>57</v>
+      </c>
+      <c r="R23" t="n">
+        <v>85</v>
+      </c>
+      <c r="S23" t="n">
+        <v>100</v>
+      </c>
+      <c r="T23" t="n">
+        <v>592</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
+      </c>
+      <c r="V23" t="n">
+        <v>2</v>
+      </c>
+      <c r="W23" t="n">
         <v>3</v>
       </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>7</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>0.905</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>0.356</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>0.436</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>1000:00</t>
         </is>
       </c>
       <c r="AO23" t="n">
-        <v>2</v>
+        <v>419.48</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>0.618</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>0.641</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.099</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>5.317</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>6.983</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="BA23" t="n">
         <v>0</v>
@@ -4065,163 +4065,163 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Rival</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C24" t="n">
-        <v>290</v>
+        <v>362</v>
       </c>
       <c r="D24" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="E24" t="n">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="F24" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G24" t="n">
-        <v>98</v>
+        <v>158</v>
       </c>
       <c r="H24" t="n">
+        <v>59</v>
+      </c>
+      <c r="I24" t="n">
+        <v>76</v>
+      </c>
+      <c r="J24" t="n">
+        <v>81</v>
+      </c>
+      <c r="K24" t="n">
+        <v>115</v>
+      </c>
+      <c r="L24" t="n">
+        <v>39</v>
+      </c>
+      <c r="M24" t="n">
+        <v>36</v>
+      </c>
+      <c r="N24" t="n">
+        <v>18</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>55</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>48</v>
+      </c>
+      <c r="R24" t="n">
+        <v>92</v>
+      </c>
+      <c r="S24" t="n">
+        <v>95</v>
+      </c>
+      <c r="T24" t="n">
+        <v>388</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>108</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>140</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="AB24" t="n">
         <v>33</v>
       </c>
-      <c r="I24" t="n">
-        <v>45</v>
-      </c>
-      <c r="J24" t="n">
-        <v>68</v>
-      </c>
-      <c r="K24" t="n">
-        <v>95</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="AC24" t="n">
+        <v>67</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="AK24" t="n">
         <v>30</v>
       </c>
-      <c r="M24" t="n">
-        <v>21</v>
-      </c>
-      <c r="N24" t="n">
-        <v>11</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>32</v>
-      </c>
-      <c r="R24" t="n">
-        <v>47</v>
-      </c>
-      <c r="S24" t="n">
-        <v>53</v>
-      </c>
-      <c r="T24" t="n">
-        <v>380</v>
-      </c>
-      <c r="U24" t="n">
-        <v>27</v>
-      </c>
-      <c r="V24" t="n">
-        <v>32</v>
-      </c>
-      <c r="W24" t="n">
-        <v>42</v>
-      </c>
-      <c r="X24" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>73</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>79</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0.924</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>47</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0.426</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>40</v>
-      </c>
       <c r="AL24" t="n">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.435</v>
+        <v>0.227</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>600:00</t>
+          <t>1000:00</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>255.8</v>
+        <v>414.44</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.636</v>
+        <v>0.465</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.654</v>
+        <v>0.504</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.134</v>
+        <v>0.873</v>
       </c>
       <c r="AS24" t="n">
         <v>0.133</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.163</v>
+        <v>0.181</v>
       </c>
       <c r="AU24" t="n">
-        <v>2</v>
+        <v>1.473</v>
       </c>
       <c r="AV24" t="n">
-        <v>5.941</v>
+        <v>5.927</v>
       </c>
       <c r="AW24" t="n">
-        <v>7.941</v>
+        <v>7.4</v>
       </c>
       <c r="AX24" t="n">
         <v>0.2</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.06</v>
+        <v>0.039</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="BA24" t="n">
         <v>0</v>
@@ -4230,271 +4230,271 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Rival</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>3</v>
-      </c>
-      <c r="C25" t="n">
-        <v>216</v>
-      </c>
-      <c r="D25" t="n">
-        <v>63</v>
-      </c>
-      <c r="E25" t="n">
-        <v>113</v>
-      </c>
-      <c r="F25" t="n">
-        <v>18</v>
-      </c>
-      <c r="G25" t="n">
-        <v>87</v>
-      </c>
-      <c r="H25" t="n">
-        <v>36</v>
-      </c>
-      <c r="I25" t="n">
-        <v>43</v>
-      </c>
-      <c r="J25" t="n">
-        <v>49</v>
-      </c>
-      <c r="K25" t="n">
-        <v>70</v>
-      </c>
-      <c r="L25" t="n">
-        <v>24</v>
-      </c>
-      <c r="M25" t="n">
-        <v>20</v>
-      </c>
-      <c r="N25" t="n">
-        <v>11</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>37</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>32</v>
-      </c>
-      <c r="R25" t="n">
-        <v>48</v>
-      </c>
-      <c r="S25" t="n">
-        <v>54</v>
-      </c>
-      <c r="T25" t="n">
-        <v>233</v>
-      </c>
-      <c r="U25" t="n">
-        <v>30</v>
-      </c>
-      <c r="V25" t="n">
-        <v>27</v>
-      </c>
-      <c r="W25" t="n">
-        <v>27</v>
-      </c>
-      <c r="X25" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>66</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>88</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>25</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>48</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>600:00</t>
-        </is>
-      </c>
-      <c r="AO25" t="n">
-        <v>255.92</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0.493</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>1.324</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>5.405</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
+          <t>--- PER GAME STATS ---</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AU25" t="inlineStr"/>
+      <c r="AV25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr"/>
+      <c r="AX25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr"/>
+      <c r="BA25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>--- PER GAME STATS ---</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr"/>
-      <c r="AO26" t="inlineStr"/>
-      <c r="AP26" t="inlineStr"/>
-      <c r="AQ26" t="inlineStr"/>
-      <c r="AR26" t="inlineStr"/>
-      <c r="AS26" t="inlineStr"/>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AU26" t="inlineStr"/>
-      <c r="AV26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr"/>
-      <c r="AX26" t="inlineStr"/>
-      <c r="AY26" t="inlineStr"/>
-      <c r="AZ26" t="inlineStr"/>
-      <c r="BA26" t="inlineStr"/>
+          <t>#0 T. WALKUP (Per Game)</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T26" t="n">
+        <v>64</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>23:05</t>
+        </is>
+      </c>
+      <c r="AO26" t="n">
+        <v>5.528</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0.901</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.411</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.833</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>3.167</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>#0 T. WALKUP (Per Game)</t>
+          <t>#1 F. NTILIKINA (Per Game)</t>
         </is>
       </c>
       <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
         <v>3</v>
       </c>
-      <c r="C27" t="n">
-        <v>9</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F27" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="G27" t="n">
-        <v>4.333</v>
-      </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>5.333</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4506,19 +4506,19 @@
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S27" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>41</v>
+        <v>-7</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -4548,7 +4548,7 @@
         <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -4563,94 +4563,94 @@
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.667</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>4.333</v>
+        <v>3</v>
       </c>
       <c r="AM27" t="n">
-        <v>0.615</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>45:28</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>6.253</v>
+        <v>4</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.857</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.857</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.439</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.214</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>5.333</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>4.667</v>
+        <v>3</v>
       </c>
       <c r="AW27" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.065</v>
+        <v>0.141</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.044</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>#1 F. NTILIKINA (Per Game)</t>
+          <t>#3 T. WARD (Per Game)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>6.333</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="G28" t="n">
-        <v>3</v>
+        <v>1.333</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
         <v>1</v>
@@ -4659,25 +4659,25 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>0.333</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>1.667</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>1.667</v>
       </c>
       <c r="R28" t="n">
-        <v>5</v>
+        <v>1.667</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="T28" t="n">
-        <v>-7</v>
+        <v>15</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -4692,19 +4692,19 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.333</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.667</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4728,76 +4728,76 @@
         <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="AL28" t="n">
-        <v>3</v>
+        <v>1.333</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>23:33</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>4</v>
+        <v>6.587</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>0.644</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>0.962</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.25</v>
+        <v>0.253</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AW28" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.08</v>
+        <v>0.289</v>
       </c>
       <c r="AY28" t="n">
-        <v>0.051</v>
+        <v>0.112</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>0.092</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>#3 T. WARD (Per Game)</t>
+          <t>#11 M. MORRIS (Per Game)</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -4809,13 +4809,13 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -4836,13 +4836,13 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -4851,19 +4851,19 @@
         <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -4903,20 +4903,20 @@
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>00:08</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.064</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
         <v>0</v>
@@ -4934,13 +4934,13 @@
         <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.061</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
         <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
         <v>0</v>
@@ -4949,65 +4949,65 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>#11 M. MORRIS (Per Game)</t>
+          <t>#14 S. VEZENKOV (Per Game)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -5022,1012 +5022,1012 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>0.278</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>24:12</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>13.616</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>0.619</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>0.636</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>0.102</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>9.833</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>10.833</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>0.268</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>#14 S. VEZENKOV (Per Game)</t>
+          <t>#16 K. PAPANIKOLAOU (Per Game)</t>
         </is>
       </c>
       <c r="B31" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>11</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AO31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV31" t="n">
         <v>3</v>
       </c>
-      <c r="C31" t="n">
-        <v>17</v>
-      </c>
-      <c r="D31" t="n">
-        <v>4</v>
-      </c>
-      <c r="E31" t="n">
-        <v>6.333</v>
-      </c>
-      <c r="F31" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="G31" t="n">
-        <v>6.333</v>
-      </c>
-      <c r="H31" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="K31" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2</v>
-      </c>
-      <c r="T31" t="n">
-        <v>55</v>
-      </c>
-      <c r="U31" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="V31" t="n">
-        <v>3</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>6</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>56:35</t>
-        </is>
-      </c>
-      <c r="AO31" t="n">
-        <v>14.44</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0.632</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.177</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>9.5</v>
-      </c>
       <c r="AW31" t="n">
-        <v>10.75</v>
+        <v>5</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.12</v>
+        <v>0.099</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.014</v>
+        <v>0.048</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.077</v>
+        <v>0.091</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.057</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>#16 K. PAPANIKOLAOU (Per Game)</t>
+          <t>#22 T. DORSEY (Per Game)</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="F32" t="n">
-        <v>1.333</v>
+        <v>0.8</v>
       </c>
       <c r="G32" t="n">
-        <v>3.333</v>
+        <v>3.8</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
-        <v>2.333</v>
+        <v>0.8</v>
       </c>
       <c r="K32" t="n">
-        <v>1.667</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="M32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>24</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>17:27</t>
+        </is>
+      </c>
+      <c r="AO32" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="AU32" t="n">
         <v>0.667</v>
       </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>2</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="T32" t="n">
-        <v>15</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>34:28</t>
-        </is>
-      </c>
-      <c r="AO32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>2.333</v>
-      </c>
       <c r="AV32" t="n">
-        <v>3.333</v>
+        <v>6.833</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.667</v>
+        <v>7.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.059</v>
+        <v>0.281</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.035</v>
+        <v>0.014</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.049</v>
+        <v>0.057</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.068</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>#22 T. DORSEY (Per Game)</t>
+          <t>#25 A. PETERS (Per Game)</t>
         </is>
       </c>
       <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="n">
+        <v>13</v>
+      </c>
+      <c r="D33" t="n">
         <v>3</v>
       </c>
-      <c r="C33" t="n">
-        <v>6.667</v>
-      </c>
-      <c r="D33" t="n">
-        <v>2.333</v>
-      </c>
       <c r="E33" t="n">
-        <v>4.667</v>
+        <v>4</v>
       </c>
       <c r="F33" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T33" t="n">
+        <v>90</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.727</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG33" t="n">
         <v>0.667</v>
       </c>
-      <c r="G33" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
+      <c r="AH33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM33" t="n">
         <v>0.667</v>
       </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="T33" t="n">
-        <v>13</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>3</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0.1</v>
-      </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>42:22</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>9.627000000000001</v>
+        <v>8.007999999999999</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.4</v>
+        <v>0.85</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.386</v>
+        <v>0.877</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.6929999999999999</v>
+        <v>1.623</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.104</v>
+        <v>0.075</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>0.467</v>
       </c>
       <c r="AU33" t="n">
-        <v>1</v>
+        <v>2.667</v>
       </c>
       <c r="AV33" t="n">
-        <v>8.333</v>
+        <v>10</v>
       </c>
       <c r="AW33" t="n">
-        <v>9.333</v>
+        <v>12.667</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.107</v>
+        <v>0.213</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>0.054</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.016</v>
+        <v>0.257</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.031</v>
+        <v>0.056</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>#25 A. PETERS (Per Game)</t>
+          <t>#33 N. MILUTINOV (Per Game)</t>
         </is>
       </c>
       <c r="B34" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D34" t="n">
         <v>3</v>
       </c>
-      <c r="C34" t="n">
-        <v>10.667</v>
-      </c>
-      <c r="D34" t="n">
-        <v>2.333</v>
-      </c>
       <c r="E34" t="n">
-        <v>3.667</v>
+        <v>5.2</v>
       </c>
       <c r="F34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4</v>
+      </c>
+      <c r="L34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T34" t="n">
+        <v>77</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>19:24</t>
+        </is>
+      </c>
+      <c r="AO34" t="n">
+        <v>6.568</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.127</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="AU34" t="n">
         <v>3</v>
       </c>
-      <c r="I34" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="K34" t="n">
-        <v>5</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="R34" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>45</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0.917</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>23:43</t>
-        </is>
-      </c>
-      <c r="AO34" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0.748</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1.368</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0.08500000000000001</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0.529</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AV34" t="n">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="AW34" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.154</v>
+        <v>0.161</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.051</v>
+        <v>0.214</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.212</v>
+        <v>0.206</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.052</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>#33 N. MILUTINOV (Per Game)</t>
+          <t>#34 C. JOSEPH (Per Game)</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C35" t="n">
-        <v>7.667</v>
+        <v>5.6</v>
       </c>
       <c r="D35" t="n">
-        <v>3.333</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>5.333</v>
+        <v>2.2</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I35" t="n">
-        <v>1.667</v>
+        <v>1.2</v>
       </c>
       <c r="J35" t="n">
-        <v>1.667</v>
+        <v>2.8</v>
       </c>
       <c r="K35" t="n">
-        <v>2.333</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>0.2</v>
       </c>
       <c r="M35" t="n">
-        <v>0.333</v>
+        <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0.333</v>
+        <v>1.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.333</v>
+        <v>1.4</v>
       </c>
       <c r="R35" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T35" t="n">
+        <v>44</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
         <v>2</v>
       </c>
-      <c r="T35" t="n">
-        <v>42</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
+      <c r="Z35" t="n">
         <v>2</v>
       </c>
-      <c r="W35" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>3.667</v>
-      </c>
       <c r="AA35" t="n">
-        <v>0.8179999999999999</v>
+        <v>1</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.667</v>
+        <v>0.2</v>
       </c>
       <c r="AC35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AO35" t="n">
+        <v>5.928</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AU35" t="n">
         <v>2</v>
       </c>
-      <c r="AD35" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>41:41</t>
-        </is>
-      </c>
-      <c r="AO35" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0.632</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>1.198</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>5</v>
-      </c>
       <c r="AV35" t="n">
-        <v>16</v>
+        <v>2.857</v>
       </c>
       <c r="AW35" t="n">
-        <v>21</v>
+        <v>4.857</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.166</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.014</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.056</v>
+        <v>0.117</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.052</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>#34 C. JOSEPH (Per Game)</t>
+          <t>#45 D. HALL (Per Game)</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C36" t="n">
-        <v>7.667</v>
+        <v>3.8</v>
       </c>
       <c r="D36" t="n">
-        <v>1.333</v>
+        <v>1.6</v>
       </c>
       <c r="E36" t="n">
-        <v>2.333</v>
+        <v>2.2</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>2.333</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T36" t="n">
+        <v>39</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z36" t="n">
         <v>2</v>
       </c>
-      <c r="I36" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" t="n">
-        <v>3</v>
-      </c>
-      <c r="K36" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="T36" t="n">
-        <v>36</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>3</v>
-      </c>
       <c r="AA36" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.333</v>
+        <v>0.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
@@ -6048,595 +6048,595 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>2.333</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>0.429</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>31:40</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AO36" t="n">
-        <v>7.547</v>
+        <v>3.216</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.607</v>
+        <v>0.727</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.675</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.016</v>
+        <v>1.182</v>
       </c>
       <c r="AS36" t="n">
-        <v>0.265</v>
+        <v>0.124</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.429</v>
+        <v>0.273</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.333</v>
+        <v>5.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>3.833</v>
+        <v>6.5</v>
       </c>
       <c r="AX36" t="n">
-        <v>0.112</v>
+        <v>0.124</v>
       </c>
       <c r="AY36" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="BA36" t="n">
         <v>0.013</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>0.09</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>#45 D. HALL (Per Game)</t>
+          <t>#77 S. MCKISSIC (Per Game)</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="D37" t="n">
-        <v>2.333</v>
+        <v>1.6</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="H37" t="n">
-        <v>0.333</v>
+        <v>0.8</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>3.333</v>
+        <v>1.2</v>
       </c>
       <c r="L37" t="n">
-        <v>1.667</v>
+        <v>0.2</v>
       </c>
       <c r="M37" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="N37" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>1.333</v>
+        <v>0.8</v>
       </c>
       <c r="T37" t="n">
         <v>33</v>
       </c>
       <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AO37" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="AP37" t="n">
         <v>0.667</v>
       </c>
-      <c r="V37" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>24:45</t>
-        </is>
-      </c>
-      <c r="AO37" t="n">
-        <v>3.773</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>0.778</v>
-      </c>
       <c r="AQ37" t="n">
-        <v>0.727</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.325</v>
+        <v>1.322</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.041</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.111</v>
+        <v>0.19</v>
       </c>
       <c r="AU37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV37" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="AW37" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.201</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.081</v>
+        <v>0.021</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.136</v>
+        <v>0.105</v>
       </c>
       <c r="BA37" t="n">
-        <v>0.02</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>#77 S. MCKISSIC (Per Game)</t>
+          <t>#88 T. JONES (Per Game)</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C38" t="n">
-        <v>8.667</v>
+        <v>2.8</v>
       </c>
       <c r="D38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T38" t="n">
+        <v>19</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="AO38" t="n">
+        <v>2.792</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0.857</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
         <v>2.333</v>
       </c>
-      <c r="E38" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="H38" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T38" t="n">
-        <v>29</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1</v>
-      </c>
-      <c r="W38" t="n">
-        <v>2</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>27:45</t>
-        </is>
-      </c>
-      <c r="AO38" t="n">
-        <v>5.773</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0.719</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0.751</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.501</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>0</v>
-      </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>2.333</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.098</v>
+        <v>0.161</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.014</v>
+        <v>0.059</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.048</v>
+        <v>0.17</v>
       </c>
       <c r="BA38" t="n">
-        <v>0.031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>#88 T. JONES (Per Game)</t>
+          <t>#94 E. FOURNIER (Per Game)</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C39" t="n">
-        <v>2.667</v>
+        <v>16.2</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="E39" t="n">
-        <v>1.667</v>
+        <v>3.6</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="H39" t="n">
-        <v>0.667</v>
+        <v>1.8</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="K39" t="n">
-        <v>1.333</v>
+        <v>4.2</v>
       </c>
       <c r="L39" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="M39" t="n">
-        <v>0.667</v>
+        <v>0.8</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>0.667</v>
+        <v>2.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.667</v>
+        <v>2.2</v>
       </c>
       <c r="R39" t="n">
-        <v>0.667</v>
+        <v>1.8</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="T39" t="n">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.333</v>
+        <v>3.2</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.667</v>
+        <v>3.2</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.667</v>
+        <v>1.8</v>
       </c>
       <c r="AD39" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG39" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>0.459</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>24:09</t>
         </is>
       </c>
       <c r="AO39" t="n">
-        <v>2.773</v>
+        <v>14.568</v>
       </c>
       <c r="AP39" t="n">
-        <v>0.6</v>
+        <v>0.632</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.633</v>
+        <v>0.655</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.962</v>
+        <v>1.112</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.24</v>
+        <v>0.151</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.4</v>
+        <v>0.158</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>1.909</v>
       </c>
       <c r="AV39" t="n">
-        <v>2.5</v>
+        <v>5.182</v>
       </c>
       <c r="AW39" t="n">
-        <v>2.5</v>
+        <v>7.091</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.094</v>
+        <v>0.287</v>
       </c>
       <c r="AY39" t="n">
-        <v>0.058</v>
+        <v>0.02</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0.097</v>
+        <v>0.174</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>0.152</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>#94 E. FOURNIER (Per Game)</t>
+          <t>Equip (Per Game)</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C40" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
         <v>2</v>
       </c>
-      <c r="E40" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="F40" t="n">
-        <v>4</v>
-      </c>
-      <c r="G40" t="n">
-        <v>8</v>
-      </c>
-      <c r="H40" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="J40" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="K40" t="n">
-        <v>4.667</v>
-      </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -6645,282 +6645,282 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>3.667</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.667</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>2.667</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.333</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.333</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.333</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.333</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>3.667</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>7.333</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>43:09</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AO40" t="n">
-        <v>13.92</v>
+        <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.706</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.713</v>
+        <v>0</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.221</v>
+        <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.144</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.08799999999999999</v>
+        <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>2.167</v>
+        <v>0</v>
       </c>
       <c r="AV40" t="n">
-        <v>5.667</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>7.833</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.151</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
         <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0.109</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
-        <v>0.146</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>TOTAL (Per Game)</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>92.2</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>20.2</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>34.8</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>13.4</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>18.4</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K41" t="n">
-        <v>2</v>
+        <v>32.2</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0.667</v>
+        <v>12</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>592</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>26.6</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>29.4</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>0.905</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>14.6</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>0.356</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>0.429</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>11.6</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>26.6</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>0.436</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:00</t>
         </is>
       </c>
       <c r="AO41" t="n">
-        <v>0</v>
+        <v>83.896</v>
       </c>
       <c r="AP41" t="n">
-        <v>0</v>
+        <v>0.618</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>0.641</v>
       </c>
       <c r="AR41" t="n">
-        <v>0</v>
+        <v>1.099</v>
       </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>0.143</v>
       </c>
       <c r="AT41" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>1.667</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>5.317</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>6.983</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AY41" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>0.161</v>
       </c>
       <c r="BA41" t="n">
         <v>0</v>
@@ -6929,65 +6929,65 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>Equip (Per Game)</t>
+          <t>Rival (Per Game)</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>18.6</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>33.6</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>31.6</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>11.8</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>15.2</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>16.2</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>18.4</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="T42" t="n">
-        <v>7</v>
+        <v>388</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -7002,422 +7002,92 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>21.6</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>0.771</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>13.4</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>0.493</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>0.346</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>26.4</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>0.227</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>200:00</t>
         </is>
       </c>
       <c r="AO42" t="n">
-        <v>0.667</v>
+        <v>82.88800000000001</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>0.465</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0</v>
+        <v>0.504</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>0.873</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>0.133</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>0.181</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>1.473</v>
       </c>
       <c r="AV42" t="n">
-        <v>0</v>
+        <v>5.927</v>
       </c>
       <c r="AW42" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>0.198</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>0.048</v>
       </c>
       <c r="AZ42" t="n">
-        <v>0</v>
+        <v>0.115</v>
       </c>
       <c r="BA42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (Per Game)</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>3</v>
-      </c>
-      <c r="C43" t="n">
-        <v>96.667</v>
-      </c>
-      <c r="D43" t="n">
-        <v>21.333</v>
-      </c>
-      <c r="E43" t="n">
-        <v>34.667</v>
-      </c>
-      <c r="F43" t="n">
-        <v>14.333</v>
-      </c>
-      <c r="G43" t="n">
-        <v>32.667</v>
-      </c>
-      <c r="H43" t="n">
-        <v>11</v>
-      </c>
-      <c r="I43" t="n">
-        <v>15</v>
-      </c>
-      <c r="J43" t="n">
-        <v>22.667</v>
-      </c>
-      <c r="K43" t="n">
-        <v>31.667</v>
-      </c>
-      <c r="L43" t="n">
-        <v>10</v>
-      </c>
-      <c r="M43" t="n">
-        <v>7</v>
-      </c>
-      <c r="N43" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>11.333</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>10.667</v>
-      </c>
-      <c r="R43" t="n">
-        <v>15.667</v>
-      </c>
-      <c r="S43" t="n">
-        <v>17.667</v>
-      </c>
-      <c r="T43" t="n">
-        <v>380</v>
-      </c>
-      <c r="U43" t="n">
-        <v>9</v>
-      </c>
-      <c r="V43" t="n">
-        <v>10.667</v>
-      </c>
-      <c r="W43" t="n">
-        <v>14</v>
-      </c>
-      <c r="X43" t="n">
-        <v>6.667</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>24.333</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>26.333</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0.924</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>6.667</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>15.667</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0.426</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>13.333</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>30.667</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO43" t="n">
-        <v>85.267</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>1.134</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>0.163</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV43" t="n">
-        <v>5.941</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>7.941</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>Rival (Per Game)</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>3</v>
-      </c>
-      <c r="C44" t="n">
-        <v>72</v>
-      </c>
-      <c r="D44" t="n">
-        <v>21</v>
-      </c>
-      <c r="E44" t="n">
-        <v>37.667</v>
-      </c>
-      <c r="F44" t="n">
-        <v>6</v>
-      </c>
-      <c r="G44" t="n">
-        <v>29</v>
-      </c>
-      <c r="H44" t="n">
-        <v>12</v>
-      </c>
-      <c r="I44" t="n">
-        <v>14.333</v>
-      </c>
-      <c r="J44" t="n">
-        <v>16.333</v>
-      </c>
-      <c r="K44" t="n">
-        <v>23.333</v>
-      </c>
-      <c r="L44" t="n">
-        <v>8</v>
-      </c>
-      <c r="M44" t="n">
-        <v>6.667</v>
-      </c>
-      <c r="N44" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>12.333</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>10.667</v>
-      </c>
-      <c r="R44" t="n">
-        <v>16</v>
-      </c>
-      <c r="S44" t="n">
-        <v>18</v>
-      </c>
-      <c r="T44" t="n">
-        <v>233</v>
-      </c>
-      <c r="U44" t="n">
-        <v>10</v>
-      </c>
-      <c r="V44" t="n">
-        <v>9</v>
-      </c>
-      <c r="W44" t="n">
-        <v>9</v>
-      </c>
-      <c r="X44" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>29.333</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO44" t="n">
-        <v>85.307</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>0.493</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>0.844</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>1.324</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>5.405</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="BA44" t="n">
         <v>0</v>
       </c>
     </row>

--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_OLYMPIACOS PIRAEUS.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_OLYMPIACOS PIRAEUS.xlsx
@@ -671,13 +671,13 @@
         <v>0.2100313479623825</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="M2" t="n">
         <v>57</v>
@@ -752,13 +752,13 @@
         <v>1.324137931034483</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.03636363636363636</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.04081632653061224</v>
+        <v>1.061224489795918</v>
       </c>
       <c r="AM2" t="n">
-        <v>3</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="AN2" t="n">
         <v>1.666666666666667</v>
@@ -801,13 +801,13 @@
         <v>0.2100313479623825</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4</v>
+        <v>10.4</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6</v>
+        <v>12.8</v>
       </c>
       <c r="M3" t="n">
         <v>11.4</v>
@@ -882,13 +882,13 @@
         <v>1.324137931034483</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.03636363636363637</v>
+        <v>0.6363636363636364</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.04081632653061224</v>
+        <v>1.061224489795918</v>
       </c>
       <c r="AM3" t="n">
-        <v>3</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="AN3" t="n">
         <v>1.666666666666667</v>
@@ -931,13 +931,13 @@
         <v>0.1809815950920245</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M4" t="n">
         <v>48</v>
@@ -1012,13 +1012,13 @@
         <v>0.740506329113924</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>0.7833333333333333</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>0.8717948717948718</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AN4" t="n">
         <v>1.472727272727273</v>
@@ -1061,13 +1061,13 @@
         <v>0.1809815950920245</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="M5" t="n">
         <v>9.6</v>
@@ -1142,13 +1142,13 @@
         <v>0.7405063291139241</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>0.7833333333333333</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>0.8717948717948718</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AN5" t="n">
         <v>1.472727272727273</v>
@@ -1486,10 +1486,10 @@
         <v>64</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1819,13 +1819,13 @@
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
         <v>7</v>
@@ -2146,16 +2146,16 @@
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="n">
         <v>21</v>
@@ -2317,10 +2317,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -2476,16 +2476,16 @@
         <v>24</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="n">
         <v>7</v>
@@ -2644,13 +2644,13 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y15" t="n">
         <v>19</v>
@@ -2806,16 +2806,16 @@
         <v>77</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y16" t="n">
         <v>18</v>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
@@ -3136,16 +3136,16 @@
         <v>39</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y18" t="n">
         <v>9</v>
@@ -3301,16 +3301,16 @@
         <v>33</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="n">
         <v>11</v>
@@ -3466,10 +3466,10 @@
         <v>19</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
@@ -3631,16 +3631,16 @@
         <v>91</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="V21" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="W21" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="X21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y21" t="n">
         <v>16</v>
@@ -3961,16 +3961,16 @@
         <v>592</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="V23" t="n">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="W23" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="Y23" t="n">
         <v>133</v>
@@ -4126,16 +4126,16 @@
         <v>388</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Y24" t="n">
         <v>108</v>
@@ -4350,10 +4350,10 @@
         <v>64</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -4683,13 +4683,13 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Y28" t="n">
         <v>2.333</v>
@@ -5010,16 +5010,16 @@
         <v>80</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Y30" t="n">
         <v>4.2</v>
@@ -5181,10 +5181,10 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Y31" t="n">
         <v>0</v>
@@ -5340,16 +5340,16 @@
         <v>24</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Y32" t="n">
         <v>1.4</v>
@@ -5508,13 +5508,13 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Y33" t="n">
         <v>3.8</v>
@@ -5670,16 +5670,16 @@
         <v>77</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="Y34" t="n">
         <v>3.6</v>
@@ -5838,7 +5838,7 @@
         <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W35" t="n">
         <v>0</v>
@@ -6000,16 +6000,16 @@
         <v>39</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
         <v>1.8</v>
@@ -6165,16 +6165,16 @@
         <v>33</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Y37" t="n">
         <v>2.2</v>
@@ -6330,10 +6330,10 @@
         <v>19</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W38" t="n">
         <v>0</v>
@@ -6495,16 +6495,16 @@
         <v>91</v>
       </c>
       <c r="U39" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="V39" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="W39" t="n">
-        <v>0.6</v>
+        <v>2.2</v>
       </c>
       <c r="X39" t="n">
-        <v>0.2</v>
+        <v>1.2</v>
       </c>
       <c r="Y39" t="n">
         <v>3.2</v>
@@ -6825,16 +6825,16 @@
         <v>592</v>
       </c>
       <c r="U41" t="n">
-        <v>0.4</v>
+        <v>7</v>
       </c>
       <c r="V41" t="n">
-        <v>0.4</v>
+        <v>10.4</v>
       </c>
       <c r="W41" t="n">
-        <v>0.6</v>
+        <v>12.8</v>
       </c>
       <c r="X41" t="n">
-        <v>0.2</v>
+        <v>7.2</v>
       </c>
       <c r="Y41" t="n">
         <v>26.6</v>
@@ -6990,16 +6990,16 @@
         <v>388</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Y42" t="n">
         <v>21.6</v>

--- a/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_OLYMPIACOS PIRAEUS.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/aggregate/AGGREGATE_OLYMPIACOS PIRAEUS.xlsx
@@ -683,13 +683,13 @@
         <v>57</v>
       </c>
       <c r="N2" t="n">
-        <v>133</v>
+        <v>66</v>
       </c>
       <c r="O2" t="n">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4608150470219436</v>
+        <v>0.2507836990595611</v>
       </c>
       <c r="Q2" t="n">
         <v>26</v>
@@ -710,25 +710,25 @@
         <v>0.06583072100313479</v>
       </c>
       <c r="W2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.03761755485893417</v>
+        <v>0.0438871473354232</v>
       </c>
       <c r="Z2" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AA2" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.4169278996865204</v>
+        <v>0.4106583072100313</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.825</v>
       </c>
       <c r="AD2" t="n">
         <v>0.3561643835616438</v>
@@ -737,13 +737,13 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.4360902255639098</v>
+        <v>0.4274809160305343</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.80952380952381</v>
+        <v>1.65</v>
       </c>
       <c r="AI2" t="n">
         <v>0.8571428571428571</v>
@@ -813,13 +813,13 @@
         <v>11.4</v>
       </c>
       <c r="N3" t="n">
-        <v>26.6</v>
+        <v>13.2</v>
       </c>
       <c r="O3" t="n">
-        <v>29.4</v>
+        <v>16</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4608150470219436</v>
+        <v>0.2507836990595612</v>
       </c>
       <c r="Q3" t="n">
         <v>5.2</v>
@@ -840,25 +840,25 @@
         <v>0.06583072100313481</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="X3" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.03761755485893417</v>
+        <v>0.0438871473354232</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>26.6</v>
+        <v>26.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.4169278996865204</v>
+        <v>0.4106583072100314</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.9047619047619049</v>
+        <v>0.825</v>
       </c>
       <c r="AD3" t="n">
         <v>0.3561643835616439</v>
@@ -867,13 +867,13 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.5</v>
+        <v>0.5714285714285715</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.4360902255639098</v>
+        <v>0.4274809160305343</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.80952380952381</v>
+        <v>1.65</v>
       </c>
       <c r="AI3" t="n">
         <v>0.8571428571428571</v>
@@ -943,13 +943,13 @@
         <v>48</v>
       </c>
       <c r="N4" t="n">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="O4" t="n">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4294478527607362</v>
+        <v>0.2484662576687117</v>
       </c>
       <c r="Q4" t="n">
         <v>33</v>
@@ -970,25 +970,25 @@
         <v>0.06134969325153374</v>
       </c>
       <c r="W4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X4" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.07975460122699386</v>
+        <v>0.09815950920245399</v>
       </c>
       <c r="Z4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA4" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4049079754601227</v>
+        <v>0.3865030674846626</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.6049382716049383</v>
       </c>
       <c r="AD4" t="n">
         <v>0.4925373134328358</v>
@@ -997,13 +997,13 @@
         <v>0.55</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3461538461538461</v>
+        <v>0.34375</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.542857142857143</v>
+        <v>1.209876543209877</v>
       </c>
       <c r="AI4" t="n">
         <v>1.1</v>
@@ -1073,13 +1073,13 @@
         <v>9.6</v>
       </c>
       <c r="N5" t="n">
-        <v>21.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>28</v>
+        <v>16.2</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4294478527607362</v>
+        <v>0.2484662576687116</v>
       </c>
       <c r="Q5" t="n">
         <v>6.6</v>
@@ -1100,25 +1100,25 @@
         <v>0.06134969325153374</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="X5" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.07975460122699386</v>
+        <v>0.09815950920245399</v>
       </c>
       <c r="Z5" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AA5" t="n">
-        <v>26.4</v>
+        <v>25.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4049079754601226</v>
+        <v>0.3865030674846626</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.6049382716049383</v>
       </c>
       <c r="AD5" t="n">
         <v>0.4925373134328358</v>
@@ -1127,19 +1127,19 @@
         <v>0.55</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.3461538461538461</v>
+        <v>0.34375</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.542857142857143</v>
+        <v>1.209876543209877</v>
       </c>
       <c r="AI5" t="n">
         <v>1.1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.7405063291139241</v>
+        <v>0.740506329113924</v>
       </c>
       <c r="AK5" t="n">
         <v>0.7833333333333333</v>
@@ -1498,10 +1498,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
         <v>1</v>
@@ -1828,13 +1828,13 @@
         <v>1</v>
       </c>
       <c r="Y10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z10" t="n">
         <v>7</v>
       </c>
-      <c r="Z10" t="n">
-        <v>8</v>
-      </c>
       <c r="AA10" t="n">
-        <v>0.875</v>
+        <v>0.857</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -2158,10 +2158,10 @@
         <v>4</v>
       </c>
       <c r="Y12" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Z12" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AA12" t="n">
         <v>1</v>
@@ -2185,22 +2185,22 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AK12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.4</v>
+        <v>0.368</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
@@ -2488,13 +2488,13 @@
         <v>6</v>
       </c>
       <c r="Y14" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.7</v>
+        <v>0.25</v>
       </c>
       <c r="AB14" t="n">
         <v>5</v>
@@ -2653,13 +2653,13 @@
         <v>6</v>
       </c>
       <c r="Y15" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="Z15" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.95</v>
+        <v>0.833</v>
       </c>
       <c r="AB15" t="n">
         <v>8</v>
@@ -2818,13 +2818,13 @@
         <v>3</v>
       </c>
       <c r="Y16" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="Z16" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.75</v>
+        <v>0.647</v>
       </c>
       <c r="AB16" t="n">
         <v>2</v>
@@ -2983,10 +2983,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Z17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AA17" t="n">
         <v>1</v>
@@ -3148,13 +3148,13 @@
         <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Z18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.9</v>
+        <v>0.857</v>
       </c>
       <c r="AB18" t="n">
         <v>2</v>
@@ -3313,10 +3313,10 @@
         <v>4</v>
       </c>
       <c r="Y19" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Z19" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AA19" t="n">
         <v>1</v>
@@ -3478,13 +3478,13 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Z20" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="AB20" t="n">
         <v>1</v>
@@ -3643,10 +3643,10 @@
         <v>6</v>
       </c>
       <c r="Y21" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Z21" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AA21" t="n">
         <v>1</v>
@@ -3670,22 +3670,22 @@
         <v>0.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AK21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL21" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.459</v>
+        <v>0.444</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
@@ -3973,13 +3973,13 @@
         <v>36</v>
       </c>
       <c r="Y23" t="n">
-        <v>133</v>
+        <v>66</v>
       </c>
       <c r="Z23" t="n">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.905</v>
+        <v>0.825</v>
       </c>
       <c r="AB23" t="n">
         <v>26</v>
@@ -4000,22 +4000,22 @@
         <v>0.429</v>
       </c>
       <c r="AH23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI23" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AK23" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AL23" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AM23" t="n">
-        <v>0.436</v>
+        <v>0.427</v>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
@@ -4138,13 +4138,13 @@
         <v>25</v>
       </c>
       <c r="Y24" t="n">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="Z24" t="n">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.771</v>
+        <v>0.605</v>
       </c>
       <c r="AB24" t="n">
         <v>33</v>
@@ -4165,22 +4165,22 @@
         <v>0.55</v>
       </c>
       <c r="AH24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI24" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.346</v>
+        <v>0.344</v>
       </c>
       <c r="AK24" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL24" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.227</v>
+        <v>0.222</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
@@ -4362,10 +4362,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="AA26" t="n">
         <v>1</v>
@@ -4692,13 +4692,13 @@
         <v>0.333</v>
       </c>
       <c r="Y28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z28" t="n">
         <v>2.333</v>
       </c>
-      <c r="Z28" t="n">
-        <v>2.667</v>
-      </c>
       <c r="AA28" t="n">
-        <v>0.875</v>
+        <v>0.857</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -5022,10 +5022,10 @@
         <v>0.8</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="AA30" t="n">
         <v>1</v>
@@ -5049,22 +5049,22 @@
         <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="AI30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>0.8</v>
       </c>
-      <c r="AJ30" t="n">
-        <v>0.75</v>
-      </c>
       <c r="AK30" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AL30" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.4</v>
+        <v>0.368</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
@@ -5352,13 +5352,13 @@
         <v>1.2</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.4</v>
+        <v>0.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.7</v>
+        <v>0.25</v>
       </c>
       <c r="AB32" t="n">
         <v>1</v>
@@ -5517,13 +5517,13 @@
         <v>1.2</v>
       </c>
       <c r="Y33" t="n">
-        <v>3.8</v>
+        <v>1</v>
       </c>
       <c r="Z33" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.95</v>
+        <v>0.833</v>
       </c>
       <c r="AB33" t="n">
         <v>1.6</v>
@@ -5682,13 +5682,13 @@
         <v>0.6</v>
       </c>
       <c r="Y34" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.75</v>
+        <v>0.647</v>
       </c>
       <c r="AB34" t="n">
         <v>0.4</v>
@@ -5847,10 +5847,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="Z35" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="AA35" t="n">
         <v>1</v>
@@ -6012,13 +6012,13 @@
         <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.9</v>
+        <v>0.857</v>
       </c>
       <c r="AB36" t="n">
         <v>0.4</v>
@@ -6177,10 +6177,10 @@
         <v>0.8</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="AA37" t="n">
         <v>1</v>
@@ -6342,13 +6342,13 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="AB38" t="n">
         <v>0.2</v>
@@ -6507,10 +6507,10 @@
         <v>1.2</v>
       </c>
       <c r="Y39" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="AA39" t="n">
         <v>1</v>
@@ -6534,22 +6534,22 @@
         <v>0.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.5</v>
+        <v>0.667</v>
       </c>
       <c r="AK39" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AL39" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AM39" t="n">
-        <v>0.459</v>
+        <v>0.444</v>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
@@ -6837,13 +6837,13 @@
         <v>7.2</v>
       </c>
       <c r="Y41" t="n">
-        <v>26.6</v>
+        <v>13.2</v>
       </c>
       <c r="Z41" t="n">
-        <v>29.4</v>
+        <v>16</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.905</v>
+        <v>0.825</v>
       </c>
       <c r="AB41" t="n">
         <v>5.2</v>
@@ -6864,22 +6864,22 @@
         <v>0.429</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AI41" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AK41" t="n">
-        <v>11.6</v>
+        <v>11.2</v>
       </c>
       <c r="AL41" t="n">
-        <v>26.6</v>
+        <v>26.2</v>
       </c>
       <c r="AM41" t="n">
-        <v>0.436</v>
+        <v>0.427</v>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
@@ -7002,13 +7002,13 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>21.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z42" t="n">
-        <v>28</v>
+        <v>16.2</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.771</v>
+        <v>0.605</v>
       </c>
       <c r="AB42" t="n">
         <v>6.6</v>
@@ -7029,22 +7029,22 @@
         <v>0.55</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AI42" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.346</v>
+        <v>0.344</v>
       </c>
       <c r="AK42" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AL42" t="n">
-        <v>26.4</v>
+        <v>25.2</v>
       </c>
       <c r="AM42" t="n">
-        <v>0.227</v>
+        <v>0.222</v>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
